--- a/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 49 D100 Spring 2024 24GO00I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 49 D100 Spring 2024 24GO00I13 Zoop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Ontario\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83BE5A5-EBDC-43E4-8A46-3A4E182A9D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6A0174-A9C9-4CF2-8662-AA465DAC4469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CE8EB46A-BE49-4DC8-AA8F-BFB4B853FC07}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE8EB46A-BE49-4DC8-AA8F-BFB4B853FC07}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId2"/>
+    <pivotCache cacheId="12" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4273,7 +4273,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{738CC515-35CF-4770-A8B3-2EBDB095FA96}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{738CC515-35CF-4770-A8B3-2EBDB095FA96}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U2:AA16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -4720,20 +4720,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17DAA10A-7CDB-4167-831D-6708376F3B43}">
   <dimension ref="A1:AA191"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="4" width="9.140625" customWidth="1"/>
-    <col min="11" max="11" width="26.42578125" customWidth="1"/>
-    <col min="21" max="21" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="2" max="4" width="9.109375" customWidth="1"/>
+    <col min="11" max="11" width="26.44140625" customWidth="1"/>
+    <col min="21" max="21" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="4" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4789,7 +4789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -5253,7 +5253,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -5525,7 +5525,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -5850,7 +5850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>1.002</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="W22" s="8"/>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="W23" s="8"/>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="V24" s="8"/>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -6801,7 +6801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -6907,7 +6907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -7119,7 +7119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -7278,7 +7278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -7331,7 +7331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>33</v>
       </c>
       <c r="N46" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O46">
         <v>1.4330000000000001</v>
@@ -7437,7 +7437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -7649,7 +7649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -7967,7 +7967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -8020,7 +8020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -8126,7 +8126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -8179,7 +8179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -8232,7 +8232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -8285,7 +8285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -8444,7 +8444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -8497,7 +8497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -8656,7 +8656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -9133,7 +9133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -9186,7 +9186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -9292,7 +9292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -9398,7 +9398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -9451,7 +9451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -9504,7 +9504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -9557,7 +9557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -9610,7 +9610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -9663,7 +9663,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -9716,7 +9716,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -9769,7 +9769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -9875,7 +9875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -9928,7 +9928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -9981,7 +9981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -10087,7 +10087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -10193,7 +10193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -10299,7 +10299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -10405,7 +10405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -10458,7 +10458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -10511,7 +10511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -10617,7 +10617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -10670,7 +10670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -10723,7 +10723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -10829,7 +10829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -10882,7 +10882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -10935,7 +10935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -10988,7 +10988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -11041,7 +11041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -11147,7 +11147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -11200,7 +11200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -11306,7 +11306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -11359,7 +11359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -11465,7 +11465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -11518,7 +11518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -11571,7 +11571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -11677,7 +11677,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -11730,7 +11730,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -11836,7 +11836,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -12101,7 +12101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -12154,7 +12154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -12260,7 +12260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -12313,7 +12313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -12631,7 +12631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -12737,7 +12737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -12790,7 +12790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -12843,7 +12843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -12896,7 +12896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -13002,7 +13002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -13055,7 +13055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -13108,7 +13108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -13161,7 +13161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -13267,7 +13267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -13320,7 +13320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -13373,7 +13373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -13426,7 +13426,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -13532,7 +13532,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -13585,7 +13585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -13638,7 +13638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -13691,7 +13691,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -13744,7 +13744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -13797,7 +13797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -13850,7 +13850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -13903,7 +13903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -13956,7 +13956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -14009,7 +14009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -14115,7 +14115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -14168,7 +14168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -14221,7 +14221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -14327,7 +14327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -14380,7 +14380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -14433,7 +14433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -14486,7 +14486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -14539,7 +14539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -14645,7 +14645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -14698,7 +14698,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -14751,7 +14751,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -14804,7 +14804,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -14857,7 +14857,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -14910,7 +14910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
         <v>18</v>
       </c>
@@ -14963,7 +14963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
         <v>18</v>
       </c>
@@ -15016,7 +15016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
         <v>18</v>
       </c>
@@ -15069,7 +15069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
         <v>18</v>
       </c>

--- a/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 49 D100 Spring 2024 24GO00I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 49 D100 Spring 2024 24GO00I13 Zoop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Ontario\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6A0174-A9C9-4CF2-8662-AA465DAC4469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B851D9A-B497-42BF-97D7-F65EC6EB5C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE8EB46A-BE49-4DC8-AA8F-BFB4B853FC07}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId2"/>
+    <pivotCache cacheId="40" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4273,7 +4273,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{738CC515-35CF-4770-A8B3-2EBDB095FA96}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{738CC515-35CF-4770-A8B3-2EBDB095FA96}" name="PivotTable1" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U2:AA16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -10929,7 +10929,7 @@
         <v>1.2529999999999999</v>
       </c>
       <c r="P112" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Q112">
         <v>1</v>
